--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23D.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23D.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>48976</t>
   </si>
@@ -109,7 +109,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
@@ -118,19 +118,22 @@
     <t>Departamento de Información y Relaciones Publicas del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
-    <t>971317E2D214D51DD5876EAAFAE8F265</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>17/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo 01 de julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no tiene inherencia en la utilización de Tiempos Oficiales por lo que hago mención de dos mensajes aclaratorios e informativos: Menasje 1:"La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales está a cargo de la Dirección General de Radio, Televisión y Cinematografía de la Secretaría de Gabernación." Mensaje 2:" La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales esta a cargo del Instituto Nacional Electoral." Por lo que no se genera información alguna.</t>
+    <t>E533B447C2147FAEE73FB43034AA56C8</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>03/07/2023</t>
+  </si>
+  <si>
+    <t>11/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo 01 de julio de 2023 al 30 de septiembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no tiene inherencia en la utilización de Tiempos Oficiales por lo que hago mención de dos mensajes aclaratorios e informativos: Menasje 1:"La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales está a cargo de la Dirección General de Radio, Televisión y Cinematografía de la Secretaría de Gabernación." Mensaje 2:" La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales esta a cargo del Instituto Nacional Electoral." Por lo que no se genera información alguna.</t>
   </si>
 </sst>
 </file>
@@ -526,11 +529,11 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="117.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="116.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="86" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -702,10 +705,10 @@
         <v>37</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
